--- a/CPRD Raw Analysis/Results/SecondaryCareAnalysis/OP/Overall/overall_bootstrap_summary_costs_encounters_SOURCE.xlsx
+++ b/CPRD Raw Analysis/Results/SecondaryCareAnalysis/OP/Overall/overall_bootstrap_summary_costs_encounters_SOURCE.xlsx
@@ -418,34 +418,34 @@
         </is>
       </c>
       <c r="B2">
-        <v>1198.49</v>
+        <v>1228.582</v>
       </c>
       <c r="C2">
-        <v>133.353</v>
+        <v>126.189</v>
       </c>
       <c r="D2">
-        <v>11.548</v>
+        <v>11.233</v>
       </c>
       <c r="E2">
-        <v>0.365</v>
+        <v>0.355</v>
       </c>
       <c r="F2">
-        <v>1176.83</v>
+        <v>1207.614</v>
       </c>
       <c r="G2">
-        <v>1222.096</v>
+        <v>1251.648</v>
       </c>
       <c r="H2">
-        <v>1175.503</v>
+        <v>1206.882</v>
       </c>
       <c r="I2">
-        <v>1220.394</v>
+        <v>1250.307</v>
       </c>
       <c r="J2">
-        <v>1177.559</v>
+        <v>1207.906</v>
       </c>
       <c r="K2">
-        <v>1222.449</v>
+        <v>1251.331</v>
       </c>
     </row>
     <row r="3">
@@ -455,34 +455,34 @@
         </is>
       </c>
       <c r="B3">
-        <v>1338.938</v>
+        <v>1372.621</v>
       </c>
       <c r="C3">
-        <v>147.892</v>
+        <v>140.959</v>
       </c>
       <c r="D3">
-        <v>12.161</v>
+        <v>11.873</v>
       </c>
       <c r="E3">
-        <v>0.385</v>
+        <v>0.375</v>
       </c>
       <c r="F3">
-        <v>1315.319</v>
+        <v>1349.502</v>
       </c>
       <c r="G3">
-        <v>1362.99</v>
+        <v>1396.042</v>
       </c>
       <c r="H3">
-        <v>1315.033</v>
+        <v>1349.026</v>
       </c>
       <c r="I3">
-        <v>1363.223</v>
+        <v>1396.151</v>
       </c>
       <c r="J3">
-        <v>1314.869</v>
+        <v>1349.243</v>
       </c>
       <c r="K3">
-        <v>1363.06</v>
+        <v>1396.367</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/SecondaryCareAnalysis/OP/Overall/overall_bootstrap_summary_costs_encounters_SOURCE.xlsx
+++ b/CPRD Raw Analysis/Results/SecondaryCareAnalysis/OP/Overall/overall_bootstrap_summary_costs_encounters_SOURCE.xlsx
@@ -418,34 +418,34 @@
         </is>
       </c>
       <c r="B2">
-        <v>1228.582</v>
+        <v>1228.282</v>
       </c>
       <c r="C2">
-        <v>126.189</v>
+        <v>124.504</v>
       </c>
       <c r="D2">
-        <v>11.233</v>
+        <v>11.158</v>
       </c>
       <c r="E2">
-        <v>0.355</v>
+        <v>0.353</v>
       </c>
       <c r="F2">
-        <v>1207.614</v>
+        <v>1207.343</v>
       </c>
       <c r="G2">
-        <v>1251.648</v>
+        <v>1251.082</v>
       </c>
       <c r="H2">
-        <v>1206.882</v>
+        <v>1206.377</v>
       </c>
       <c r="I2">
-        <v>1250.307</v>
+        <v>1251.214</v>
       </c>
       <c r="J2">
-        <v>1207.906</v>
+        <v>1206.281</v>
       </c>
       <c r="K2">
-        <v>1251.331</v>
+        <v>1251.118</v>
       </c>
     </row>
     <row r="3">
@@ -455,34 +455,34 @@
         </is>
       </c>
       <c r="B3">
-        <v>1372.621</v>
+        <v>1372.287</v>
       </c>
       <c r="C3">
-        <v>140.959</v>
+        <v>143</v>
       </c>
       <c r="D3">
-        <v>11.873</v>
+        <v>11.958</v>
       </c>
       <c r="E3">
-        <v>0.375</v>
+        <v>0.378</v>
       </c>
       <c r="F3">
-        <v>1349.502</v>
+        <v>1349.047</v>
       </c>
       <c r="G3">
-        <v>1396.042</v>
+        <v>1395.923</v>
       </c>
       <c r="H3">
-        <v>1349.026</v>
+        <v>1348.45</v>
       </c>
       <c r="I3">
-        <v>1396.151</v>
+        <v>1395.903</v>
       </c>
       <c r="J3">
-        <v>1349.243</v>
+        <v>1348.868</v>
       </c>
       <c r="K3">
-        <v>1396.367</v>
+        <v>1396.322</v>
       </c>
     </row>
   </sheetData>
